--- a/consent_forms/027_child_medical_procedure_permission_form--consent_forms.xlsx
+++ b/consent_forms/027_child_medical_procedure_permission_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -912,8 +912,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -941,12 +941,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Parent', 'value': 'parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'legal_guardian',_'value':_'guardian'}</t>
+          <t>legal_guardian</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Legal Guardian', 'value': 'guardian'}</t>
+          <t>Legal Guardian</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other_authorized_representative',_'value':_'other'}</t>
+          <t>other_authorized_representative</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other Authorized Representative', 'value': 'other'}</t>
+          <t>Other Authorized Representative</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_followed_fasting_instructions',_'value':_true}</t>
+          <t>yes_-_followed_fasting_instructions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Followed Fasting Instructions', 'value': True}</t>
+          <t>Yes - Followed Fasting Instructions</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_has_eaten',_'value':_false}</t>
+          <t>no_-_has_eaten</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'No - Has Eaten', 'value': False}</t>
+          <t>No - Has Eaten</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable_to_this_procedure',_'value':_'na'}</t>
+          <t>not_applicable_to_this_procedure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable to this procedure', 'value': 'na'}</t>
+          <t>Not Applicable to this procedure</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_i_understand',_'value':_true}</t>
+          <t>yes_-_i_understand</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - I Understand', 'value': True}</t>
+          <t>Yes - I Understand</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_i_need_more_information',_'value':_false}</t>
+          <t>no_-_i_need_more_information</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'No - I Need More Information', 'value': False}</t>
+          <t>No - I Need More Information</t>
         </is>
       </c>
     </row>
